--- a/EstablecimientoSalud/excels/PUNO-EL_COLLAO-ILAVE.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-EL_COLLAO-ILAVE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>33147</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-16.0825395</t>
+          <t>-16.0854612</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-69.6384724</t>
+          <t>-69.6378272</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>POLICLINICO GM</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO "SUMA JAKAAA "</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PASAJE PASAJE 28 DE NOVIEMBRE NÂ° 126 DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+          <t>ALTIPLANO S/N  BARRIO  ALTO ALIANZA  CHUNTA CCOLLO DISTRITO ILAVE DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>33147</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -642,35 +642,1461 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-16.0854612</t>
+          <t>-16.163695</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-69.6378272</t>
+          <t>-69.58242</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO "SUMA JAKAAA "</t>
+          <t>ANCOAMAYA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALTIPLANO S/N  BARRIO  ALTO ALIANZA  CHUNTA CCOLLO DISTRITO ILAVE DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+          <t>OTROS CENTRO POBLADO ANCOAMAYA DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3039</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-16.14109167</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-69.60130833</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CHUCARAYA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO DE CHUCARAYA DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-16.24135167</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-69.63672833</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CHURO LOPEZ</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>OTROS VILLA CHURO LOPEZ DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-16.17615167</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-69.62963</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PACCO RISALAZO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO PACCO RISALAZO DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10885</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-16.08228664</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-69.63465119</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ENFERMERIA DEL BIM 59 - ILAVE</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AVENIDA AV. EJERCITO S/N ILAVE NUMERO S/N DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3122</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-16.17571333</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-69.54051833</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SANTA  ANA TARUCANI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD DE SANTA ANA TARUCANI DISTRITO PUTINA PROVINCIA SAN ANTONIO DE PUTINA DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3046</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-16.006641</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-69.470691</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PHARATA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO DE PHARATA DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>13851</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-16.08307142</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-69.63814689</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>METROPOLITANO ILAVE</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AVENIDA AV. ATAHUALPA S/N NUMERO S/N DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>I-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-16.00761833</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-69.55761167</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SULLCACATURA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO SULLCACATURA CENTRO POBLADO SULLCACATURA ACORA PUNO PUNO</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3047</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-16.00955833</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-69.52996333</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ROSACANI</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO DE ROSACANI DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-16.11263333</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-69.60233</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CHILACOLLO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD CHILACOLLO DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2997</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-16.251315</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-69.63151833</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>KANKORA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO KANCCORA YACANGO DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3041</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-16.20257833</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-69.66091167</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>JACHOCCO HUARACCO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO JACHOCCO HUARACCO DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-16.03595333</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-69.51492833</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PACUNCANI CALLATA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO PACUNCANI CALLATA DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3043</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-16.0827192</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-69.6377489</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>OCONA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO OCONA DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3121</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-16.20257833</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-69.66091167</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PICOTANI</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD DE PICOTANI DISTRITO PUTINA PROVINCIA SAN ANTONIO DE PUTINA DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3033</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-16.03054312</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-69.56772482</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CAMICACHI</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>OTROS PUEBLO DE CAMICACHI DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-16.07998286</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-69.63971694</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CANGALLI</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO CANGALLI DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-16.024355</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-69.58613333</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>LAQUI</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO LAQUI CENTRO POBLADO LAQUI ACORA PUNO PUNO</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6702</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-16.19331667</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-69.60208333</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CORARACA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO CORARACA DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-16.16774833</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-69.68833</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CHIJICHAYA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO CHIJICHAYA DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3049</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-16.0825395</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-69.6384724</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SIRAYA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO SIRAYA DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-16.17571333</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-69.54051833</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>MULLACONTIHUECO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO MULLA CONTIHUECO DISTRITO ILAVE PROVINCIA EL COLLAO DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2966</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EL COLLAO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-16.087442</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-69.588116</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>TAYPE</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>JR. PITUMARCA S/N COMUNIDAD TAYPE NUMERO S/N DISTRITO AYAPATA PROVINCIA CARABAYA DEPARTAMENTO PUNO</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>210501</t>
         </is>

--- a/EstablecimientoSalud/excels/PUNO-EL_COLLAO-ILAVE.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-EL_COLLAO-ILAVE.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>9218</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-16.0825395</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>33147</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-16.0854612</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>3034</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-16.163695</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>3039</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-16.14109167</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>3040</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-16.24135167</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>3044</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-16.17615167</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>10885</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-16.08228664</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>3122</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-16.17571333</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>3046</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-16.006641</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>13851</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-16.08307142</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>3212</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-16.00761833</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>3047</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-16.00955833</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>3038</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-16.11263333</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>2997</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-16.251315</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>3041</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-16.20257833</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>3045</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-16.03595333</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>3043</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-16.0827192</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>3121</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-16.20257833</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>3033</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-16.03054312</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>3035</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-16.07998286</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>3208</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-16.024355</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>6702</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-16.19331667</t>
@@ -1846,40 +1736,35 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>3037</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-16.16774833</t>
@@ -1908,40 +1793,35 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>3049</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-16.0825395</t>
@@ -1970,40 +1850,35 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>3042</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-16.17571333</t>
@@ -2032,40 +1907,35 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EL_COLLAO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ILAVE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2966</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>210501</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>EL COLLAO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ILAVE</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-16.087442</t>
@@ -2094,11 +1964,6 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>210501</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/PUNO-EL_COLLAO-ILAVE.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-EL_COLLAO-ILAVE.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/EstablecimientoSalud/excels/PUNO-EL_COLLAO-ILAVE.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-EL_COLLAO-ILAVE.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EL_COLLAO</t>
+          <t>EL COLLAO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
